--- a/태화라이온스 일정표.xlsx
+++ b/태화라이온스 일정표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBFBF3E-7882-4473-9729-669D417EB53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF295B81-CE0D-4DB9-A222-FA4EA09A3BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="885" yWindow="2355" windowWidth="21600" windowHeight="11295" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>5일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -146,6 +146,22 @@
   </si>
   <si>
     <t>1부회장 및 신입회원 연수회</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10월</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>급식봉사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">합동월례회 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -551,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21159285-A4BD-44FD-9E4A-15FD187A27CD}">
-  <dimension ref="A2:B19"/>
+  <dimension ref="A2:B24"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="40.25" customWidth="1"/>
@@ -685,6 +701,38 @@
         <v>24</v>
       </c>
     </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/태화라이온스 일정표.xlsx
+++ b/태화라이온스 일정표.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF295B81-CE0D-4DB9-A222-FA4EA09A3BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95951BDC-408C-438E-9F82-4E5C548DA80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>5일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -162,6 +162,10 @@
   </si>
   <si>
     <t xml:space="preserve">합동월례회 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이사회, 골프회 정기라운딩</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -714,7 +718,7 @@
         <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">

--- a/태화라이온스 일정표.xlsx
+++ b/태화라이온스 일정표.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\이재원\클로드코딩\태화라이온스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95951BDC-408C-438E-9F82-4E5C548DA80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D62689F4-2AA1-4569-97C2-BBDC7B55D2A1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>5일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -166,13 +165,29 @@
   </si>
   <si>
     <t>이사회, 골프회 정기라운딩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">울산공업축제 먹거리 부스 (지구행사) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총재배 공프대회 (지구행사)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -227,7 +242,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -236,6 +251,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -570,8 +588,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21159285-A4BD-44FD-9E4A-15FD187A27CD}">
-  <dimension ref="A2:B24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:B26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="40.25" customWidth="1"/>
@@ -715,30 +733,47 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B25" s="1" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>